--- a/Input Excel Sheets/Point Performance Requirements/Requirements_Input_ACDesign.xlsx
+++ b/Input Excel Sheets/Point Performance Requirements/Requirements_Input_ACDesign.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tyty/Documents/MATLAB/AircraftDesignToolbox-Feb23/MAIN/Input Excel Sheets/Point Performance Requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C40AAC-F0AE-9546-973A-F36D3535D1DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC38B710-F1FC-2D4F-B096-1C887F1EBDF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="3" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="1" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
   </bookViews>
   <sheets>
     <sheet name="Templates" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="12" r:id="rId2"/>
+    <sheet name="BuffAir" sheetId="12" r:id="rId2"/>
     <sheet name="MD80" sheetId="9" r:id="rId3"/>
     <sheet name="B717" sheetId="11" r:id="rId4"/>
   </sheets>
@@ -1894,7 +1894,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="3">
-        <v>7800</v>
+        <v>11000</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>18</v>
@@ -1909,7 +1909,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="I3" s="25">
-        <v>8000</v>
+        <v>7300</v>
       </c>
       <c r="J3" s="11" t="s">
         <v>40</v>
@@ -1954,7 +1954,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="3">
-        <v>7800</v>
+        <v>11000</v>
       </c>
       <c r="E5" s="3">
         <v>2.88</v>
@@ -1966,7 +1966,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="H5" s="25">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>39</v>
@@ -2151,14 +2151,14 @@
         <v>0.85199999999999998</v>
       </c>
       <c r="D11" s="3">
-        <v>37000</v>
+        <v>35000</v>
       </c>
       <c r="E11" s="3">
         <f>E9</f>
         <v>0.76</v>
       </c>
       <c r="F11" s="3">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="G11" s="3" t="str">
         <f>E3</f>
@@ -4484,27 +4484,27 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A6:A1048576">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="12" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:K1">
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="11" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:F184 G14:K186">
-    <cfRule type="expression" dxfId="2" priority="5">
+    <cfRule type="expression" dxfId="10" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:K2 C3:G3 J3:K3 C4:K4 C5:E5 I5:K5">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="9" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:K13">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7196,27 +7196,27 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A6:A1048576">
-    <cfRule type="expression" dxfId="12" priority="12">
+    <cfRule type="expression" dxfId="7" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:K1">
-    <cfRule type="expression" dxfId="11" priority="9">
+    <cfRule type="expression" dxfId="6" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:F184 G14:K186">
-    <cfRule type="expression" dxfId="10" priority="17">
+    <cfRule type="expression" dxfId="5" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:K2 C3:G3 J3:K3 C4:K4 C5:E5 I5:K5">
-    <cfRule type="expression" dxfId="9" priority="8">
+    <cfRule type="expression" dxfId="4" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:K13">
-    <cfRule type="expression" dxfId="8" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10068,18 +10068,18 @@
       <c r="K198" s="41"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:B1 D1:K1 B2:K4 C5:K5 F13:K19 B14:E19 A20:K1048576 B6:K11">
-    <cfRule type="expression" dxfId="7" priority="3">
+  <conditionalFormatting sqref="A1:B1 D1:K1 B2:K4 C5:K5 B6:K11 F13:K19 B14:E19 A20:K1048576">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D12">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
